--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260618.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260618.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.10%</t>
+          <t>27.60%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.18%</t>
+          <t>8.96%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.26%</t>
+          <t>8.50%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.38%</t>
+          <t>7.69%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>5.12%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -814,14 +814,14 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>4,918,877</t>
+          <t>170,275,514</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>22,790</t>
+          <t>9,410</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>9,410</t>
+          <t>22,790</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>84,003,340</t>
+          <t>148,265</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -1188,51 +1188,51 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>148,265</t>
+          <t>18,691</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>18,691</t>
+          <t>13,865</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1254,95 +1254,51 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>13,865</t>
+          <t>50,510</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>50,510</t>
+          <t>969,568</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>94,695,000</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>-971,793</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
